--- a/Luban/Config/Datas/Levels/L01/SceneInfo.xlsx
+++ b/Luban/Config/Datas/Levels/L01/SceneInfo.xlsx
@@ -1443,7 +1443,7 @@
         <v>100</v>
       </c>
       <c r="M4" s="0" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N4" s="0" t="n">
         <v>2500</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves</t>
+          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves; diagram-maze-20261028; zero-leak (initialHp=1)</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L01/SceneInfo.xlsx
+++ b/Luban/Config/Datas/Levels/L01/SceneInfo.xlsx
@@ -1443,7 +1443,7 @@
         <v>100</v>
       </c>
       <c r="M4" s="0" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N4" s="0" t="n">
         <v>2500</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Q4" s="0" t="inlineStr">
         <is>
-          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves; diagram-maze-20261028; zero-leak (initialHp=1)</t>
+          <t>M1 13x7; obstacles=0; no-build=0; open-route building; stage=1; preset=中等; 25 clearable waves; diagram-maze-20261028; playerHp=10 (2026-10-29)</t>
         </is>
       </c>
     </row>
